--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>134238932</v>
       </c>
       <c r="B28" t="n">
-        <v>58231</v>
+        <v>58262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 24289-2026 artfynd.xlsx
+++ b/artfynd/A 24289-2026 artfynd.xlsx
@@ -3698,7 +3698,7 @@
         <v>134238932</v>
       </c>
       <c r="B28" t="n">
-        <v>58262</v>
+        <v>58264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
